--- a/reference/dictionaries/GEN.xlsx
+++ b/reference/dictionaries/GEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j.humphreys\Documents\Development\EHR-BSI\reference\dictionaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CE7539-BA91-440D-9F94-75E741C76C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA534A22-6F7E-443A-993A-EB157C022E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="4370" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4800" yWindow="800" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dictionary" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="160">
   <si>
     <t>raw_column_name</t>
   </si>
@@ -37,9 +37,6 @@
   </si>
   <si>
     <t>Sex</t>
-  </si>
-  <si>
-    <t>DateOfSpecCollection</t>
   </si>
   <si>
     <t>Specimen</t>
@@ -866,7 +863,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -874,7 +871,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -882,7 +879,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -890,130 +887,130 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1033,331 +1030,331 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>22</v>
-      </c>
-      <c r="C1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
         <v>38</v>
       </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
         <v>46</v>
       </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
         <v>48</v>
       </c>
-      <c r="B15" t="s">
-        <v>49</v>
-      </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
         <v>50</v>
       </c>
-      <c r="B16" t="s">
-        <v>51</v>
-      </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
         <v>53</v>
       </c>
-      <c r="B18" t="s">
-        <v>54</v>
-      </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
         <v>59</v>
       </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
         <v>64</v>
       </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" t="s">
         <v>66</v>
       </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
         <v>68</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>69</v>
-      </c>
-      <c r="C29" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1377,546 +1374,546 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" t="s">
         <v>74</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>75</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>76</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>77</v>
-      </c>
-      <c r="E1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
         <v>79</v>
-      </c>
-      <c r="B2" t="s">
-        <v>80</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
         <v>84</v>
       </c>
-      <c r="C4" t="s">
-        <v>85</v>
-      </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
         <v>87</v>
       </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" t="s">
         <v>90</v>
       </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
         <v>92</v>
       </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" t="s">
         <v>94</v>
       </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
         <v>96</v>
       </c>
-      <c r="C11" t="s">
-        <v>97</v>
-      </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
         <v>98</v>
       </c>
-      <c r="C12" t="s">
-        <v>99</v>
-      </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" t="s">
         <v>100</v>
       </c>
-      <c r="C13" t="s">
-        <v>101</v>
-      </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" t="s">
         <v>102</v>
       </c>
-      <c r="C14" t="s">
-        <v>103</v>
-      </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" t="s">
         <v>104</v>
       </c>
-      <c r="C15" t="s">
-        <v>105</v>
-      </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" t="s">
         <v>106</v>
       </c>
-      <c r="C16" t="s">
-        <v>107</v>
-      </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" t="s">
         <v>108</v>
       </c>
-      <c r="C17" t="s">
-        <v>109</v>
-      </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" t="s">
         <v>110</v>
       </c>
-      <c r="C18" t="s">
-        <v>111</v>
-      </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
         <v>112</v>
       </c>
-      <c r="C19" t="s">
-        <v>113</v>
-      </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s">
         <v>114</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>115</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>116</v>
       </c>
-      <c r="D20" t="s">
-        <v>117</v>
-      </c>
       <c r="E20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
         <v>118</v>
       </c>
-      <c r="C21" t="s">
-        <v>119</v>
-      </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" t="s">
         <v>120</v>
       </c>
-      <c r="C22" t="s">
-        <v>121</v>
-      </c>
       <c r="D22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" t="s">
         <v>122</v>
       </c>
-      <c r="C23" t="s">
-        <v>123</v>
-      </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" t="s">
         <v>125</v>
       </c>
-      <c r="C25" t="s">
-        <v>126</v>
-      </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" t="s">
         <v>127</v>
       </c>
-      <c r="C26" t="s">
-        <v>128</v>
-      </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" t="s">
         <v>129</v>
       </c>
-      <c r="C27" t="s">
-        <v>130</v>
-      </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" t="s">
         <v>131</v>
       </c>
-      <c r="C28" t="s">
-        <v>132</v>
-      </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
         <v>116</v>
       </c>
-      <c r="D29" t="s">
-        <v>117</v>
-      </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" t="s">
         <v>134</v>
       </c>
-      <c r="C30" t="s">
-        <v>135</v>
-      </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" t="s">
         <v>136</v>
       </c>
-      <c r="C31" t="s">
-        <v>137</v>
-      </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" t="s">
         <v>138</v>
       </c>
-      <c r="C32" t="s">
-        <v>139</v>
-      </c>
       <c r="D32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
